--- a/output/pdf_financials_xlsx/CSR.xlsx
+++ b/output/pdf_financials_xlsx/CSR.xlsx
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.672</v>
+        <v>-0.672</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.284298</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.672</v>
+        <v>-0.672</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.284298</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.672</v>
+        <v>-0.672</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-1.284298</v>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-22.4</v>
+        <v>22.4</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>32.10745</v>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.672</v>
+        <v>-0.672</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.284298</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.672</v>
+        <v>-0.672</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.284298</v>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.581802</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.031125</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.057553</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.82871</v>
       </c>
     </row>
     <row r="93">
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>14.35118</v>
       </c>
     </row>
     <row r="119">
@@ -3606,7 +3606,11 @@
           <t>Warrant reserve 6 (d)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3988,7 +3992,11 @@
           <t>Warrant reserve 7 (d)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4170,7 +4178,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.581802</v>
       </c>
@@ -4308,7 +4320,11 @@
           <t>Impairment of deferred acquisition cost and exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -8598,10 +8614,10 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0.672</v>
+        <v>-0.672</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>1.284298</v>
+        <v>-1.284298</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CSR.xlsx
+++ b/output/pdf_financials_xlsx/CSR.xlsx
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.084941</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00038</v>
       </c>
     </row>
     <row r="13">
@@ -946,10 +946,10 @@
         <v>-1.284298</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.855149</v>
+        <v>-0.94009</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.855149</v>
+        <v>-0.855529</v>
       </c>
     </row>
     <row r="28">
@@ -984,10 +984,10 @@
         <v>-1.284298</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.855149</v>
+        <v>-0.94009</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.855149</v>
+        <v>-0.855529</v>
       </c>
     </row>
     <row r="30">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.664243</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>3.413738</v>
@@ -1086,7 +1086,7 @@
         <v>0.620215</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.351825</v>
       </c>
     </row>
     <row r="35">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.664243</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>3.413738</v>
@@ -1124,7 +1124,7 @@
         <v>0.620215</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.351825</v>
       </c>
     </row>
     <row r="37">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.664243</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.0121</v>
@@ -1352,7 +1352,7 @@
         <v>0.058155</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.406365</v>
+        <v>0.05454</v>
       </c>
     </row>
     <row r="49">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
